--- a/docs/项目成本、进度及绩效管理追踪表v1.1.xlsx
+++ b/docs/项目成本、进度及绩效管理追踪表v1.1.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang-bl\工作\项目管理程序\RE_ 【Project Management Tool】项目成本、进度及绩效管理追踪表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CEE93F-2E42-4614-AD04-1E838DDB7D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B833F35-B9EA-43C3-B299-44680D254987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="项目成本、进度及绩效管理表-示例表" sheetId="2" r:id="rId1"/>
-    <sheet name="附件1：项目成本、进度及绩效管理表 " sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
   <si>
     <t>子项目1</t>
   </si>
@@ -536,7 +535,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -566,15 +565,51 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -582,6 +617,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -605,15 +649,6 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -621,45 +656,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -955,33 +951,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="53" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
     </row>
     <row r="2" spans="1:5" ht="35.5" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="12" t="s">
+      <c r="C3" s="40"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="11" t="s">
         <v>39</v>
       </c>
     </row>
@@ -989,12 +985,12 @@
       <c r="A4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="12" t="s">
+      <c r="C4" s="40"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="11" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1002,12 +998,12 @@
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="12" t="s">
+      <c r="C5" s="40"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="11" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1015,12 +1011,12 @@
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="12" t="s">
+      <c r="C6" s="40"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="11" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1028,17 +1024,17 @@
       <c r="A7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="18" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1050,36 +1046,28 @@
       <c r="D8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="20" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="31"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="10">
-        <v>20</v>
-      </c>
-      <c r="C9" s="10">
-        <v>30</v>
-      </c>
-      <c r="D9" s="10">
-        <v>6</v>
-      </c>
-      <c r="E9" s="33"/>
+        <v>1</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="10">
-        <v>9000</v>
-      </c>
-      <c r="C10" s="10">
-        <v>7000</v>
-      </c>
-      <c r="D10" s="10">
-        <v>12000</v>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="4" t="s">
         <v>32</v>
       </c>
@@ -1088,11 +1076,11 @@
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="21">
-        <v>5000</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23"/>
+      <c r="B11" s="36">
+        <v>123</v>
+      </c>
+      <c r="C11" s="37"/>
+      <c r="D11" s="38"/>
       <c r="E11" s="4" t="s">
         <v>7</v>
       </c>
@@ -1101,12 +1089,12 @@
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="21">
-        <f>(B9*B10)+(C9*C10)+(D9*D10)</f>
-        <v>462000</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="23"/>
+      <c r="B12" s="36">
+        <f>((B9*B10)+(C9*C10)+(D9*D10))/8</f>
+        <v>625</v>
+      </c>
+      <c r="C12" s="37"/>
+      <c r="D12" s="38"/>
       <c r="E12" s="5" t="s">
         <v>9</v>
       </c>
@@ -1115,9 +1103,9 @@
       <c r="A13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
       <c r="E13" s="4" t="s">
         <v>55</v>
       </c>
@@ -1127,13 +1115,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C14" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D14" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>11</v>
@@ -1143,12 +1131,12 @@
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="24">
-        <f>SUM(B14:D14)/SUM(B9:D9)</f>
-        <v>0.375</v>
-      </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="26"/>
+      <c r="B15" s="23">
+        <f>IFERROR(SUM(B14:D14)/SUM(B9:D9),"")</f>
+        <v>3</v>
+      </c>
+      <c r="C15" s="24"/>
+      <c r="D15" s="25"/>
       <c r="E15" s="5" t="s">
         <v>13</v>
       </c>
@@ -1157,18 +1145,18 @@
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="14">
-        <f>B15*B12</f>
-        <v>173250</v>
-      </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
+      <c r="B16" s="26">
+        <f>MIN(B15,100%)*B12</f>
+        <v>625</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
       <c r="E16" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="18" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -1180,33 +1168,33 @@
       <c r="D17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="31"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" s="9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D18" s="9">
-        <v>6</v>
-      </c>
-      <c r="E18" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="14">
         <f>SUM(B18:D18)/SUM(B9:D9)</f>
-        <v>0.375</v>
-      </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="38"/>
+        <v>21</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="22"/>
       <c r="E19" s="5" t="s">
         <v>13</v>
       </c>
@@ -1215,12 +1203,12 @@
       <c r="A20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="24">
-        <f>B19*B12</f>
-        <v>173250</v>
-      </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="26"/>
+      <c r="B20" s="26">
+        <f>MIN(B19,100%)*B12</f>
+        <v>625</v>
+      </c>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
       <c r="E20" s="5" t="s">
         <v>13</v>
       </c>
@@ -1229,12 +1217,12 @@
       <c r="A21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="26">
         <f>SUM(B18:D18)/8*5000</f>
         <v>13125</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="28"/>
       <c r="E21" s="4" t="s">
         <v>22</v>
       </c>
@@ -1243,12 +1231,12 @@
       <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="39">
+      <c r="B22" s="29">
         <f>B20-B21</f>
-        <v>160125</v>
-      </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="41"/>
+        <v>-12500</v>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="31"/>
       <c r="E22" s="4" t="s">
         <v>24</v>
       </c>
@@ -1257,12 +1245,12 @@
       <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="14">
         <f>B20-B16</f>
         <v>0</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="36"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16"/>
       <c r="E23" s="4" t="s">
         <v>26</v>
       </c>
@@ -1271,12 +1259,12 @@
       <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="17">
         <f>B20/B21</f>
-        <v>13.2</v>
-      </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="36"/>
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16"/>
       <c r="E24" s="4" t="s">
         <v>28</v>
       </c>
@@ -1285,59 +1273,50 @@
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="37">
+      <c r="B25" s="17">
         <f>B20/B16</f>
         <v>1</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16"/>
       <c r="E25" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="12" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="12" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="12" t="s">
         <v>52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
@@ -1351,337 +1330,15 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="E8:E9"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B852E063-E775-46DD-BAFA-05632FA12394}">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="30.08984375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="23.36328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="59.1796875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="53" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-    </row>
-    <row r="2" spans="1:5" ht="35.5" customHeight="1">
-      <c r="A2" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A8" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="31"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="33"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="20">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="20">
-      <c r="A13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="24" t="e">
-        <f>SUM(B13:D13)/SUM(B9:D9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="14" t="e">
-        <f>B14*B12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A16" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="31"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="33"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="34" t="e">
-        <f>SUM(B17:D17)/SUM(B9:D9)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="24" t="e">
-        <f>B18*B12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="20">
-      <c r="A20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="14">
-        <f>SUM(B17:D17)/8*5000</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="39" t="e">
-        <f>B19-B20</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="34" t="e">
-        <f>B19-B15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="37" t="e">
-        <f>B19/B20</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="37" t="e">
-        <f>B19/B15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="22">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
